--- a/Result/checksun_type/感測器_模組.xlsx
+++ b/Result/checksun_type/感測器_模組.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>41.82</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>44.24</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>48.88</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>44.24</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>48.88</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>13866223.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>14006133.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>14006133.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>12648509.3</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>24320696.58</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>24320696.58</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-7775.681584024802</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>13866223</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>13866223.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>41.33</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>44.46</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>49.11</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>44.46</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>49.11</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>29444731.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>13396437.4</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>13396437.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>15603287.4</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>26176334.2</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>26176334.2</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>62018.19883899577</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>29444731</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>29444731.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>41.15</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>44.72</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>49.41</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>44.72</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>49.41</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>5812770.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>10126744.6</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>10126744.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>13659462.7</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>26334778.56</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>26334778.56</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-1509617.050515225</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>5812770</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>5812770.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>41.65</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>45.12</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>49.74</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>45.12</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>49.74</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>11652789.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>10039474.6</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>10039474.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>14090576.6</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>28022915.42</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>28022915.42</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-1168899.547788568</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>11652789</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>11652789.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>42.49</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>45.55</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>50.13</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>45.55</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>50.13</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>9254154.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>10142828.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>10142828.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>14282953.5</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>29323837.7</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>29323837.7</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-1266130.167186609</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>9254154</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>9254154.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>43.2</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>45.95</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>50.51</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>45.95</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>50.51</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>10817743.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>11290885.2</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>11290885.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>14088287.4</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>30846889.58</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>30846889.58</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-1102815.510355718</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>10817743</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>10817743.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>44.29</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>46.39</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>50.92</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>46.39</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>50.92</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>13096267.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>17810137.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>17810137.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>14094650.9</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>35046372.82</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>35046372.82</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-997649.9823703133</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>13096267</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>13096267.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>44.77</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>46.72</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>51.32</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>46.72</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>51.32</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>5376420.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>17192180.8</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>17192180.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>14173411.2</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>41560575.68</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>41560575.68</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-1055910.72873508</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>5376420</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>5376420.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>44.86</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>46.98</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>51.68</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>46.98</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>51.68</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>12169558.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>18141678.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>18141678.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>14783110.6</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>63447588.58</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>63447588.58</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-274302.804658493</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>12169558</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>12169558.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>44.92</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>47.21</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>51.98</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>47.21</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>51.98</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>14994438.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>18423078.6</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>18423078.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>14824346.7</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>70558395.84</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>70558395.84</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>124240.2584744319</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>14994438</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>14994438.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>45.03</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>47.4</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>52.28</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>47.4</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>52.28</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>43414004.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>16885689.6</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>16885689.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>15139529.9</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>72385410.04</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>72385410.04000001</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>386484.6251473799</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>43414004</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>43414004.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>121.5</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>123.98</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>119.29</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>123.98</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>119.29</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>116792257.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>156567321.4</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>156567321.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>189454064.4</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>318150407.34</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>318150407.34</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-35640807.2288911</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>116792257</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>116792257.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>121.3</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>123.78</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>119.06</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>123.78</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>119.06</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>143570356.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>190225454.4</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>190225454.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>215742345.5</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>318733821.76</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>318733821.76</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-33370636.02417654</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>143570356</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>143570356.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>120.8</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>123.58</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>118.88</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>123.58</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>118.88</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>136096754.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>206130143.4</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>206130143.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>221377285.3</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>318478020.68</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>318478020.68</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-31804807.90943512</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>136096754</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>136096754.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>121.3</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>123.58</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>118.73</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>123.58</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>118.73</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>166072395.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>203391625.4</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>203391625.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>240690842.7</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>318219735.08</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>318219735.08</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-27631281.53446758</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>166072395</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>166072395.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>122.3</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>123.58</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>118.63</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>123.58</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>118.63</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>220304845.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>213645726.0</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>213645726</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>249224824.6</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>318339495.48</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>318339495.48</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-23893945.33685437</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>220304845</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>220304845.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>123.6</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>123.42</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>118.47</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>123.42</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>118.47</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>285082922.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>222340807.4</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>222340807.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>250119491.9</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>316878790.8</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>316878790.8</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-23512158.07823354</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>285082922</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>285082922.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>124.6</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>123.1</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>118.31</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>123.1</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>118.31</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>223093801.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>241259236.6</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>241259236.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>251423710.6</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>315242401.56</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>315242401.56</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-29067536.02740973</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>223093801</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>223093801.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>125.6</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>122.78</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>118.16</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>122.78</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>118.16</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>122404164.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>236624427.2</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>236624427.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>278228999.2</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>313300516.2</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>313300516.2</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-29323972.41811109</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>122404164</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>122404164.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>126.0</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>122.28</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>117.91</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>122.28</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>117.91</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>217342898.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>277990060.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>277990060</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>338438970.1</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>312973362.38</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>312973362.38</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-17854849.99703753</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>217342898</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>217342898.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>125.4</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>121.6</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>117.66</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>121.6</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>117.66</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>263780252.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>284803923.2</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>284803923.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>409270685.2</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>312412010.72</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>312412010.72</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-11004723.39560974</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>263780252</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>263780252.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>125.2</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>120.62</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>117.36</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>120.62</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>117.36</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>379675068.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>277898176.4</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>277898176.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>437448534.2</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>311595701.46</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>311595701.46</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-5801233.20086962</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>379675068</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>379675068.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>76.6</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>76.74</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>72.7</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>76.73999999999999</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>72.7</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>10866.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>22805.8</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>22805.8</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>24824.4</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>35440.92</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>35440.92</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-3885.075831923583</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>10866</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>10866.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>77.0</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>77.14</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>72.47</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>77.14</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>72.47</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>17378.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>27706.6</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>27706.6</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>24765.7</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>35335.7</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>35335.7</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-3149.155131571762</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>17378</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>17378.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>77.26</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>77.32</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>72.23</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>77.31999999999999</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>72.23</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>15223.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>29440.6</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>29440.6</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>24659.5</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>35124.82</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>35124.82</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-2683.0843049416</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>15223</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>15223.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>76.78</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>77.34</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>71.99</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>77.34</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>71.98999999999999</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>45420.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>33913.8</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>33913.8</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>24919.9</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>35385.58</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>35385.58</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-1690.551541722016</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>45420</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>45420.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>76.18</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>77.04</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>71.74</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>77.04000000000001</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>71.73999999999999</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>25142.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>29029.0</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>29029</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>22596.6</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>34755.56</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>34755.56</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-3447.66361063255</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>25142</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>25142.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>75.36</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>76.87</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>71.49</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>76.87</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>71.48999999999999</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>35370.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>26843.0</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>26843</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>22428.2</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>34604.28</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>34604.28</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-3662.050008696431</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>35370</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>35370.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>75.2</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>76.91</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>71.24</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>76.91</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>71.23999999999999</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>26048.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>21824.8</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>21824.8</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>20128.6</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>34252.9</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>34252.9</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-4933.385934191385</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>26048</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>26048.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>74.91999999999999</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>77.08</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>70.95</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>77.08</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>70.95</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>37589.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>19878.4</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>19878.4</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>19679.1</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>33981.94</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>33981.94</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-5574.602044391628</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>37589</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>37589.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>75.1</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>76.96</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>70.72</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>76.95999999999999</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>70.72</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>20996.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>15926.0</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>15926</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>18147.3</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>34130.62</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>34130.62</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-7528.067843092274</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>20996</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>20996.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>75.72</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>76.7</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>70.42</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>76.7</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>70.42</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>14212.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>16164.2</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>16164.2</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>20662.1</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>33992.8</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>33992.8</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-8272.052275411334</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>14212</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>14212.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>76.24000000000001</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>76.48</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>70.11</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>76.48</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>70.11</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>10279.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>18013.4</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>18013.4</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>25789.2</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>33780.52</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>33780.52</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-8312.599597459583</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>10279</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>10279.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>40.06</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>40.74</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>38.34</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>40.74</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>38.34</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>220929.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>308262.6</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>308262.6</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>525128.6</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>553146.32</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>553146.3199999999</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>-103678.2479606807</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>220929</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>220929.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>40.93</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>40.69</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>38.24</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>40.69</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>38.24</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>203433.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>336685.0</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>336685</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>817991.7</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>553429.18</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>553429.1800000001</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>-91031.04056706117</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>203433</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>203433.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>41.87</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>40.56</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>38.13</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>40.56</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>38.13</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>219162.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>392234.0</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>392234</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>1053458.6</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>552802.24</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>552802.24</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>-67837.9214130668</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>219162</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>219162.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>43.23</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>40.5</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>38.03</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>40.5</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>38.03</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>433245.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>551133.6</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>551133.6</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>1154537.3</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>552940.56</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>552940.5600000001</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>-33967.36114260822</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>433245</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>433245.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>44.13</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>40.46</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>37.94</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>40.46</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>37.94</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>464544.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>584805.6</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>584805.6</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>1142553.9</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>554651.52</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>554651.52</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>-7305.190715431352</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>464544</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>464544.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>44.52</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>40.19</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>37.75</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>40.19</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>37.75</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>363041.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>741994.6</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>741994.6</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>1120906.4</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>550504.28</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>550504.28</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>27691.05956322944</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>363041</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>363041.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>45.53</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>39.98</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>37.54</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>39.98</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>37.54</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>481178.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>1299298.4</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>1299298.4</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>1097459.1</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>545802.54</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>545802.54</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>87572.0578340583</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>481178</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>481178.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>45.84</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>39.7</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>37.31</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>39.7</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>37.31</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>1013660.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>1714683.2</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>1714683.2</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>1068516.1</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>538423.64</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>538423.64</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>157331.2318697403</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>1013660</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>1013660.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>44.97</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>39.33</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>37.04</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>39.33</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>37.04</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>601605.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>1757941.0</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>1757941</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>985126.9</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>520887.4</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>520887.4</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>194316.5793539381</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>601605</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>601605.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>43.7</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>39.02</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>36.83</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>39.02</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>36.83</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>1250489.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>1700302.2</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>1700302.2</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>952637.1</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>512978.0</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>512978</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>284361.66221158</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>1250489</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>1250489.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>42.0</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>38.52</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>36.6</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>38.52</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>36.6</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>3149560.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>1499818.2</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>1499818.2</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>884156.4</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>505646.14</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>505646.14</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>333318.4355006547</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>3149560</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>3149560.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>203.0</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>217.92</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>229.57</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>217.92</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>229.57</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>246990.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>261303.6</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>261303.6</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>360072.2</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>1087687.9</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>1087687.9</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>-60756.27700912725</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>246990</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>246990.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>201.2</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>219.42</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>229.64</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>219.42</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>229.64</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>188584.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>277235.2</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>277235.2</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>364259.9</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>1109012.44</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>1109012.44</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>-62901.108610934</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>188584</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>188584.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>200.9</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>221.0</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>229.9</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>221</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>229.9</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>266834.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>327128.4</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>327128.4</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>378625.9</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>1132112.48</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>1132112.48</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>-57460.89987741027</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>266834</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>266834.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>203.5</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>223.02</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>230.31</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>223.02</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>230.31</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>328496.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>351582.6</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>351582.6</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>393659.8</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>1170503.62</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>1170503.62</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>-56020.92669104022</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>328496</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>328496.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>206.5</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>225.2</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>230.45</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>225.2</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>230.45</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>275614.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>419383.0</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>419383</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>399217.9</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>1181679.14</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>1181679.14</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>-58569.71761440305</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>275614</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>275614.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>209.8</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>227.1</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>230.35</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>227.1</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>230.35</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>326648.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>458840.8</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>458840.8</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>399885.8</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>1187183.2</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>1187183.2</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>-54453.1433044069</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>326648</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>326648.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>214.9</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>229.28</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>230.34</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>229.28</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>230.34</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>438050.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>451284.6</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>451284.6</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>403006.7</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>1190565.96</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>1190565.96</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>-52095.49631496938</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>438050</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>438050.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>219.1</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>230.98</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>230.29</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>230.98</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>230.29</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>389105.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>430123.4</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>430123.4</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>398138.1</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>1191948.4</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>1191948.4</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>-58802.80431880965</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>389105</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>389105.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>222.5</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>232.15</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>229.96</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>232.15</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>229.96</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>667498.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>435737.0</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>435737</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>393344.8</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>1189336.42</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>1189336.42</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>-61040.46559862403</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>667498</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>667498.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>225.1</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>233.28</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>229.57</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>233.28</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>229.57</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>472903.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>379052.8</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>379052.8</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>373683.5</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>1181965.28</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>1181965.28</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>-91884.92936983652</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>472903</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>472903.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>226.8</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>233.52</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>229.07</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>233.52</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>229.07</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>288867.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>340930.8</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>340930.8</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>402140.3</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>1178670.4</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>1178670.4</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>-111817.3801369317</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>288867</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>288867.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24853,7 +24523,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
@@ -25037,15 +24707,11 @@
           <t>23.63</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
-        <is>
-          <t>24.42</t>
-        </is>
-      </c>
-      <c r="AN57" t="inlineStr">
-        <is>
-          <t>26.01</t>
-        </is>
+      <c r="AM57" t="n">
+        <v>24.42</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>26.01</v>
       </c>
       <c r="AO57" t="inlineStr">
         <is>
@@ -25092,20 +24758,16 @@
           <t>69398365.0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>46175655.8</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>46175655.8</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>40727993.5</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>194676121.56</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>194676121.56</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24784,10 @@
           <t>-6011750.455637693</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>69398365</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>69398365.0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
@@ -25289,7 +24953,7 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
@@ -25473,15 +25137,11 @@
           <t>23.42</t>
         </is>
       </c>
-      <c r="AM58" t="inlineStr">
-        <is>
-          <t>24.49</t>
-        </is>
-      </c>
-      <c r="AN58" t="inlineStr">
-        <is>
-          <t>25.98</t>
-        </is>
+      <c r="AM58" t="n">
+        <v>24.49</v>
+      </c>
+      <c r="AN58" t="n">
+        <v>25.98</v>
       </c>
       <c r="AO58" t="inlineStr">
         <is>
@@ -25528,20 +25188,16 @@
           <t>40606624.0</t>
         </is>
       </c>
-      <c r="AX58" t="inlineStr">
-        <is>
-          <t>40014316.2</t>
-        </is>
+      <c r="AX58" t="n">
+        <v>40014316.2</v>
       </c>
       <c r="AY58" t="inlineStr">
         <is>
           <t>41687883.7</t>
         </is>
       </c>
-      <c r="AZ58" t="inlineStr">
-        <is>
-          <t>195169236.84</t>
-        </is>
+      <c r="AZ58" t="n">
+        <v>195169236.84</v>
       </c>
       <c r="BA58" t="inlineStr">
         <is>
@@ -25558,8 +25214,10 @@
           <t>-9065902.528399438</t>
         </is>
       </c>
-      <c r="BD58" t="n">
-        <v>40606624</v>
+      <c r="BD58" t="inlineStr">
+        <is>
+          <t>40606624.0</t>
+        </is>
       </c>
       <c r="BE58" t="inlineStr">
         <is>
@@ -25725,7 +25383,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
@@ -25909,15 +25567,11 @@
           <t>23.48</t>
         </is>
       </c>
-      <c r="AM59" t="inlineStr">
-        <is>
-          <t>24.64</t>
-        </is>
-      </c>
-      <c r="AN59" t="inlineStr">
-        <is>
-          <t>25.97</t>
-        </is>
+      <c r="AM59" t="n">
+        <v>24.64</v>
+      </c>
+      <c r="AN59" t="n">
+        <v>25.97</v>
       </c>
       <c r="AO59" t="inlineStr">
         <is>
@@ -25964,20 +25618,16 @@
           <t>33681849.0</t>
         </is>
       </c>
-      <c r="AX59" t="inlineStr">
-        <is>
-          <t>39637812.8</t>
-        </is>
+      <c r="AX59" t="n">
+        <v>39637812.8</v>
       </c>
       <c r="AY59" t="inlineStr">
         <is>
           <t>51965661.4</t>
         </is>
       </c>
-      <c r="AZ59" t="inlineStr">
-        <is>
-          <t>195984000.1</t>
-        </is>
+      <c r="AZ59" t="n">
+        <v>195984000.1</v>
       </c>
       <c r="BA59" t="inlineStr">
         <is>
@@ -25994,8 +25644,10 @@
           <t>-10020365.29204483</t>
         </is>
       </c>
-      <c r="BD59" t="n">
-        <v>33681849</v>
+      <c r="BD59" t="inlineStr">
+        <is>
+          <t>33681849.0</t>
+        </is>
       </c>
       <c r="BE59" t="inlineStr">
         <is>
@@ -26161,7 +25813,7 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
@@ -26345,15 +25997,11 @@
           <t>23.88</t>
         </is>
       </c>
-      <c r="AM60" t="inlineStr">
-        <is>
-          <t>24.85</t>
-        </is>
-      </c>
-      <c r="AN60" t="inlineStr">
-        <is>
-          <t>25.98</t>
-        </is>
+      <c r="AM60" t="n">
+        <v>24.85</v>
+      </c>
+      <c r="AN60" t="n">
+        <v>25.98</v>
       </c>
       <c r="AO60" t="inlineStr">
         <is>
@@ -26400,20 +26048,16 @@
           <t>49106509.0</t>
         </is>
       </c>
-      <c r="AX60" t="inlineStr">
-        <is>
-          <t>38566967.2</t>
-        </is>
+      <c r="AX60" t="n">
+        <v>38566967.2</v>
       </c>
       <c r="AY60" t="inlineStr">
         <is>
           <t>52615128.9</t>
         </is>
       </c>
-      <c r="AZ60" t="inlineStr">
-        <is>
-          <t>195992723.02</t>
-        </is>
+      <c r="AZ60" t="n">
+        <v>195992723.02</v>
       </c>
       <c r="BA60" t="inlineStr">
         <is>
@@ -26430,8 +26074,10 @@
           <t>-10284073.15825091</t>
         </is>
       </c>
-      <c r="BD60" t="n">
-        <v>49106509</v>
+      <c r="BD60" t="inlineStr">
+        <is>
+          <t>49106509.0</t>
+        </is>
       </c>
       <c r="BE60" t="inlineStr">
         <is>
@@ -26597,7 +26243,7 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -26781,15 +26427,11 @@
           <t>24.26</t>
         </is>
       </c>
-      <c r="AM61" t="inlineStr">
-        <is>
-          <t>25.06</t>
-        </is>
-      </c>
-      <c r="AN61" t="inlineStr">
-        <is>
-          <t>25.98</t>
-        </is>
+      <c r="AM61" t="n">
+        <v>25.06</v>
+      </c>
+      <c r="AN61" t="n">
+        <v>25.98</v>
       </c>
       <c r="AO61" t="inlineStr">
         <is>
@@ -26836,20 +26478,16 @@
           <t>38084932.0</t>
         </is>
       </c>
-      <c r="AX61" t="inlineStr">
-        <is>
-          <t>35331650.4</t>
-        </is>
+      <c r="AX61" t="n">
+        <v>35331650.4</v>
       </c>
       <c r="AY61" t="inlineStr">
         <is>
           <t>52705529.4</t>
         </is>
       </c>
-      <c r="AZ61" t="inlineStr">
-        <is>
-          <t>195762947.24</t>
-        </is>
+      <c r="AZ61" t="n">
+        <v>195762947.24</v>
       </c>
       <c r="BA61" t="inlineStr">
         <is>
@@ -26866,8 +26504,10 @@
           <t>-11946152.49717921</t>
         </is>
       </c>
-      <c r="BD61" t="n">
-        <v>38084932</v>
+      <c r="BD61" t="inlineStr">
+        <is>
+          <t>38084932.0</t>
+        </is>
       </c>
       <c r="BE61" t="inlineStr">
         <is>
@@ -27033,7 +26673,7 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
@@ -27217,15 +26857,11 @@
           <t>24.53</t>
         </is>
       </c>
-      <c r="AM62" t="inlineStr">
-        <is>
-          <t>25.22</t>
-        </is>
-      </c>
-      <c r="AN62" t="inlineStr">
-        <is>
-          <t>25.95</t>
-        </is>
+      <c r="AM62" t="n">
+        <v>25.22</v>
+      </c>
+      <c r="AN62" t="n">
+        <v>25.95</v>
       </c>
       <c r="AO62" t="inlineStr">
         <is>
@@ -27272,20 +26908,16 @@
           <t>38591667.0</t>
         </is>
       </c>
-      <c r="AX62" t="inlineStr">
-        <is>
-          <t>35280331.2</t>
-        </is>
+      <c r="AX62" t="n">
+        <v>35280331.2</v>
       </c>
       <c r="AY62" t="inlineStr">
         <is>
           <t>51774555.3</t>
         </is>
       </c>
-      <c r="AZ62" t="inlineStr">
-        <is>
-          <t>196053683.56</t>
-        </is>
+      <c r="AZ62" t="n">
+        <v>196053683.56</v>
       </c>
       <c r="BA62" t="inlineStr">
         <is>
@@ -27302,8 +26934,10 @@
           <t>-12713019.99932038</t>
         </is>
       </c>
-      <c r="BD62" t="n">
-        <v>38591667</v>
+      <c r="BD62" t="inlineStr">
+        <is>
+          <t>38591667.0</t>
+        </is>
       </c>
       <c r="BE62" t="inlineStr">
         <is>
@@ -27469,7 +27103,7 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
@@ -27653,15 +27287,11 @@
           <t>25.11</t>
         </is>
       </c>
-      <c r="AM63" t="inlineStr">
-        <is>
-          <t>25.44</t>
-        </is>
-      </c>
-      <c r="AN63" t="inlineStr">
-        <is>
-          <t>25.96</t>
-        </is>
+      <c r="AM63" t="n">
+        <v>25.44</v>
+      </c>
+      <c r="AN63" t="n">
+        <v>25.96</v>
       </c>
       <c r="AO63" t="inlineStr">
         <is>
@@ -27708,20 +27338,16 @@
           <t>38724107.0</t>
         </is>
       </c>
-      <c r="AX63" t="inlineStr">
-        <is>
-          <t>43361451.2</t>
-        </is>
+      <c r="AX63" t="n">
+        <v>43361451.2</v>
       </c>
       <c r="AY63" t="inlineStr">
         <is>
           <t>53384515.1</t>
         </is>
       </c>
-      <c r="AZ63" t="inlineStr">
-        <is>
-          <t>197488634.64</t>
-        </is>
+      <c r="AZ63" t="n">
+        <v>197488634.64</v>
       </c>
       <c r="BA63" t="inlineStr">
         <is>
@@ -27738,8 +27364,10 @@
           <t>-13408801.60954632</t>
         </is>
       </c>
-      <c r="BD63" t="n">
-        <v>38724107</v>
+      <c r="BD63" t="inlineStr">
+        <is>
+          <t>38724107.0</t>
+        </is>
       </c>
       <c r="BE63" t="inlineStr">
         <is>
@@ -27905,7 +27533,7 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
@@ -28089,15 +27717,11 @@
           <t>25.59</t>
         </is>
       </c>
-      <c r="AM64" t="inlineStr">
-        <is>
-          <t>25.56</t>
-        </is>
-      </c>
-      <c r="AN64" t="inlineStr">
-        <is>
-          <t>25.94</t>
-        </is>
+      <c r="AM64" t="n">
+        <v>25.56</v>
+      </c>
+      <c r="AN64" t="n">
+        <v>25.94</v>
       </c>
       <c r="AO64" t="inlineStr">
         <is>
@@ -28144,20 +27768,16 @@
           <t>28327621.0</t>
         </is>
       </c>
-      <c r="AX64" t="inlineStr">
-        <is>
-          <t>64293510.0</t>
-        </is>
+      <c r="AX64" t="n">
+        <v>64293510</v>
       </c>
       <c r="AY64" t="inlineStr">
         <is>
           <t>53134957.6</t>
         </is>
       </c>
-      <c r="AZ64" t="inlineStr">
-        <is>
-          <t>197699079.6</t>
-        </is>
+      <c r="AZ64" t="n">
+        <v>197699079.6</v>
       </c>
       <c r="BA64" t="inlineStr">
         <is>
@@ -28174,8 +27794,10 @@
           <t>-13938079.56667101</t>
         </is>
       </c>
-      <c r="BD64" t="n">
-        <v>28327621</v>
+      <c r="BD64" t="inlineStr">
+        <is>
+          <t>28327621.0</t>
+        </is>
       </c>
       <c r="BE64" t="inlineStr">
         <is>
@@ -28341,7 +27963,7 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
@@ -28525,15 +28147,11 @@
           <t>25.52</t>
         </is>
       </c>
-      <c r="AM65" t="inlineStr">
-        <is>
-          <t>25.58</t>
-        </is>
-      </c>
-      <c r="AN65" t="inlineStr">
-        <is>
-          <t>25.88</t>
-        </is>
+      <c r="AM65" t="n">
+        <v>25.58</v>
+      </c>
+      <c r="AN65" t="n">
+        <v>25.88</v>
       </c>
       <c r="AO65" t="inlineStr">
         <is>
@@ -28580,20 +28198,16 @@
           <t>32929925.0</t>
         </is>
       </c>
-      <c r="AX65" t="inlineStr">
-        <is>
-          <t>66663290.6</t>
-        </is>
+      <c r="AX65" t="n">
+        <v>66663290.6</v>
       </c>
       <c r="AY65" t="inlineStr">
         <is>
           <t>54706545.9</t>
         </is>
       </c>
-      <c r="AZ65" t="inlineStr">
-        <is>
-          <t>197755621.26</t>
-        </is>
+      <c r="AZ65" t="n">
+        <v>197755621.26</v>
       </c>
       <c r="BA65" t="inlineStr">
         <is>
@@ -28610,8 +28224,10 @@
           <t>-13082493.16375375</t>
         </is>
       </c>
-      <c r="BD65" t="n">
-        <v>32929925</v>
+      <c r="BD65" t="inlineStr">
+        <is>
+          <t>32929925.0</t>
+        </is>
       </c>
       <c r="BE65" t="inlineStr">
         <is>
@@ -28777,7 +28393,7 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
@@ -28961,15 +28577,11 @@
           <t>25.35</t>
         </is>
       </c>
-      <c r="AM66" t="inlineStr">
-        <is>
-          <t>25.62</t>
-        </is>
-      </c>
-      <c r="AN66" t="inlineStr">
-        <is>
-          <t>25.82</t>
-        </is>
+      <c r="AM66" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="AN66" t="n">
+        <v>25.82</v>
       </c>
       <c r="AO66" t="inlineStr">
         <is>
@@ -29016,20 +28628,16 @@
           <t>37828336.0</t>
         </is>
       </c>
-      <c r="AX66" t="inlineStr">
-        <is>
-          <t>70079408.4</t>
-        </is>
+      <c r="AX66" t="n">
+        <v>70079408.40000001</v>
       </c>
       <c r="AY66" t="inlineStr">
         <is>
           <t>58159640.7</t>
         </is>
       </c>
-      <c r="AZ66" t="inlineStr">
-        <is>
-          <t>197616845.6</t>
-        </is>
+      <c r="AZ66" t="n">
+        <v>197616845.6</v>
       </c>
       <c r="BA66" t="inlineStr">
         <is>
@@ -29046,8 +28654,10 @@
           <t>-11886098.97516645</t>
         </is>
       </c>
-      <c r="BD66" t="n">
-        <v>37828336</v>
+      <c r="BD66" t="inlineStr">
+        <is>
+          <t>37828336.0</t>
+        </is>
       </c>
       <c r="BE66" t="inlineStr">
         <is>
@@ -29213,7 +28823,7 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
@@ -29397,15 +29007,11 @@
           <t>25.03</t>
         </is>
       </c>
-      <c r="AM67" t="inlineStr">
-        <is>
-          <t>25.62</t>
-        </is>
-      </c>
-      <c r="AN67" t="inlineStr">
-        <is>
-          <t>25.76</t>
-        </is>
+      <c r="AM67" t="n">
+        <v>25.62</v>
+      </c>
+      <c r="AN67" t="n">
+        <v>25.76</v>
       </c>
       <c r="AO67" t="inlineStr">
         <is>
@@ -29452,20 +29058,16 @@
           <t>78997267.0</t>
         </is>
       </c>
-      <c r="AX67" t="inlineStr">
-        <is>
-          <t>68268779.4</t>
-        </is>
+      <c r="AX67" t="n">
+        <v>68268779.40000001</v>
       </c>
       <c r="AY67" t="inlineStr">
         <is>
           <t>64193506.3</t>
         </is>
       </c>
-      <c r="AZ67" t="inlineStr">
-        <is>
-          <t>197596036.22</t>
-        </is>
+      <c r="AZ67" t="n">
+        <v>197596036.22</v>
       </c>
       <c r="BA67" t="inlineStr">
         <is>
@@ -29482,8 +29084,10 @@
           <t>-10277290.63521439</t>
         </is>
       </c>
-      <c r="BD67" t="n">
-        <v>78997267</v>
+      <c r="BD67" t="inlineStr">
+        <is>
+          <t>78997267.0</t>
+        </is>
       </c>
       <c r="BE67" t="inlineStr">
         <is>
@@ -29649,7 +29253,7 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
@@ -29833,15 +29437,11 @@
           <t>156.3</t>
         </is>
       </c>
-      <c r="AM68" t="inlineStr">
-        <is>
-          <t>164.85</t>
-        </is>
-      </c>
-      <c r="AN68" t="inlineStr">
-        <is>
-          <t>168.36</t>
-        </is>
+      <c r="AM68" t="n">
+        <v>164.85</v>
+      </c>
+      <c r="AN68" t="n">
+        <v>168.36</v>
       </c>
       <c r="AO68" t="inlineStr">
         <is>
@@ -29888,20 +29488,16 @@
           <t>3170553681.0</t>
         </is>
       </c>
-      <c r="AX68" t="inlineStr">
-        <is>
-          <t>4138082091.0</t>
-        </is>
+      <c r="AX68" t="n">
+        <v>4138082091</v>
       </c>
       <c r="AY68" t="inlineStr">
         <is>
           <t>4268507640.2</t>
         </is>
       </c>
-      <c r="AZ68" t="inlineStr">
-        <is>
-          <t>6060043081.46</t>
-        </is>
+      <c r="AZ68" t="n">
+        <v>6060043081.46</v>
       </c>
       <c r="BA68" t="inlineStr">
         <is>
@@ -29918,8 +29514,10 @@
           <t>-263552895.6884155</t>
         </is>
       </c>
-      <c r="BD68" t="n">
-        <v>3170553681</v>
+      <c r="BD68" t="inlineStr">
+        <is>
+          <t>3170553681.0</t>
+        </is>
       </c>
       <c r="BE68" t="inlineStr">
         <is>
@@ -30085,7 +29683,7 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
@@ -30269,15 +29867,11 @@
           <t>155.3</t>
         </is>
       </c>
-      <c r="AM69" t="inlineStr">
-        <is>
-          <t>166.68</t>
-        </is>
-      </c>
-      <c r="AN69" t="inlineStr">
-        <is>
-          <t>168.5</t>
-        </is>
+      <c r="AM69" t="n">
+        <v>166.68</v>
+      </c>
+      <c r="AN69" t="n">
+        <v>168.5</v>
       </c>
       <c r="AO69" t="inlineStr">
         <is>
@@ -30324,20 +29918,16 @@
           <t>3561255788.0</t>
         </is>
       </c>
-      <c r="AX69" t="inlineStr">
-        <is>
-          <t>4508528303.2</t>
-        </is>
+      <c r="AX69" t="n">
+        <v>4508528303.2</v>
       </c>
       <c r="AY69" t="inlineStr">
         <is>
           <t>4128239206.8</t>
         </is>
       </c>
-      <c r="AZ69" t="inlineStr">
-        <is>
-          <t>6523283246.84</t>
-        </is>
+      <c r="AZ69" t="n">
+        <v>6523283246.84</v>
       </c>
       <c r="BA69" t="inlineStr">
         <is>
@@ -30354,8 +29944,10 @@
           <t>-197408387.5697174</t>
         </is>
       </c>
-      <c r="BD69" t="n">
-        <v>3561255788</v>
+      <c r="BD69" t="inlineStr">
+        <is>
+          <t>3561255788.0</t>
+        </is>
       </c>
       <c r="BE69" t="inlineStr">
         <is>
@@ -30521,7 +30113,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
@@ -30705,15 +30297,11 @@
           <t>155.3</t>
         </is>
       </c>
-      <c r="AM70" t="inlineStr">
-        <is>
-          <t>168.38</t>
-        </is>
-      </c>
-      <c r="AN70" t="inlineStr">
-        <is>
-          <t>168.5</t>
-        </is>
+      <c r="AM70" t="n">
+        <v>168.38</v>
+      </c>
+      <c r="AN70" t="n">
+        <v>168.5</v>
       </c>
       <c r="AO70" t="inlineStr">
         <is>
@@ -30760,20 +30348,16 @@
           <t>5330763891.0</t>
         </is>
       </c>
-      <c r="AX70" t="inlineStr">
-        <is>
-          <t>5326173063.4</t>
-        </is>
+      <c r="AX70" t="n">
+        <v>5326173063.4</v>
       </c>
       <c r="AY70" t="inlineStr">
         <is>
           <t>4050371893.2</t>
         </is>
       </c>
-      <c r="AZ70" t="inlineStr">
-        <is>
-          <t>6516029437.64</t>
-        </is>
+      <c r="AZ70" t="n">
+        <v>6516029437.64</v>
       </c>
       <c r="BA70" t="inlineStr">
         <is>
@@ -30790,8 +30374,10 @@
           <t>-137726873.5940866</t>
         </is>
       </c>
-      <c r="BD70" t="n">
-        <v>5330763891</v>
+      <c r="BD70" t="inlineStr">
+        <is>
+          <t>5330763891.0</t>
+        </is>
       </c>
       <c r="BE70" t="inlineStr">
         <is>
@@ -30957,7 +30543,7 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
@@ -31141,15 +30727,11 @@
           <t>156.8</t>
         </is>
       </c>
-      <c r="AM71" t="inlineStr">
-        <is>
-          <t>169.72</t>
-        </is>
-      </c>
-      <c r="AN71" t="inlineStr">
-        <is>
-          <t>168.21</t>
-        </is>
+      <c r="AM71" t="n">
+        <v>169.72</v>
+      </c>
+      <c r="AN71" t="n">
+        <v>168.21</v>
       </c>
       <c r="AO71" t="inlineStr">
         <is>
@@ -31196,20 +30778,16 @@
           <t>3892624091.0</t>
         </is>
       </c>
-      <c r="AX71" t="inlineStr">
-        <is>
-          <t>4843786138.2</t>
-        </is>
+      <c r="AX71" t="n">
+        <v>4843786138.2</v>
       </c>
       <c r="AY71" t="inlineStr">
         <is>
           <t>3728171837.0</t>
         </is>
       </c>
-      <c r="AZ71" t="inlineStr">
-        <is>
-          <t>6576214335.28</t>
-        </is>
+      <c r="AZ71" t="n">
+        <v>6576214335.28</v>
       </c>
       <c r="BA71" t="inlineStr">
         <is>
@@ -31226,8 +30804,10 @@
           <t>-237138904.8933973</t>
         </is>
       </c>
-      <c r="BD71" t="n">
-        <v>3892624091</v>
+      <c r="BD71" t="inlineStr">
+        <is>
+          <t>3892624091.0</t>
+        </is>
       </c>
       <c r="BE71" t="inlineStr">
         <is>
@@ -31393,7 +30973,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -31577,15 +31157,11 @@
           <t>158.6</t>
         </is>
       </c>
-      <c r="AM72" t="inlineStr">
-        <is>
-          <t>170.58</t>
-        </is>
-      </c>
-      <c r="AN72" t="inlineStr">
-        <is>
-          <t>167.82</t>
-        </is>
+      <c r="AM72" t="n">
+        <v>170.58</v>
+      </c>
+      <c r="AN72" t="n">
+        <v>167.82</v>
       </c>
       <c r="AO72" t="inlineStr">
         <is>
@@ -31632,20 +31208,16 @@
           <t>4735213004.0</t>
         </is>
       </c>
-      <c r="AX72" t="inlineStr">
-        <is>
-          <t>4739633072.6</t>
-        </is>
+      <c r="AX72" t="n">
+        <v>4739633072.6</v>
       </c>
       <c r="AY72" t="inlineStr">
         <is>
           <t>3540693680.5</t>
         </is>
       </c>
-      <c r="AZ72" t="inlineStr">
-        <is>
-          <t>6556873375.6</t>
-        </is>
+      <c r="AZ72" t="n">
+        <v>6556873375.6</v>
       </c>
       <c r="BA72" t="inlineStr">
         <is>
@@ -31662,8 +31234,10 @@
           <t>-216600438.7176485</t>
         </is>
       </c>
-      <c r="BD72" t="n">
-        <v>4735213004</v>
+      <c r="BD72" t="inlineStr">
+        <is>
+          <t>4735213004.0</t>
+        </is>
       </c>
       <c r="BE72" t="inlineStr">
         <is>
@@ -31829,7 +31403,7 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -32013,15 +31587,11 @@
           <t>159.5</t>
         </is>
       </c>
-      <c r="AM73" t="inlineStr">
-        <is>
-          <t>170.95</t>
-        </is>
-      </c>
-      <c r="AN73" t="inlineStr">
-        <is>
-          <t>167.23</t>
-        </is>
+      <c r="AM73" t="n">
+        <v>170.95</v>
+      </c>
+      <c r="AN73" t="n">
+        <v>167.23</v>
       </c>
       <c r="AO73" t="inlineStr">
         <is>
@@ -32068,20 +31638,16 @@
           <t>5022784742.0</t>
         </is>
       </c>
-      <c r="AX73" t="inlineStr">
-        <is>
-          <t>4398933189.4</t>
-        </is>
+      <c r="AX73" t="n">
+        <v>4398933189.4</v>
       </c>
       <c r="AY73" t="inlineStr">
         <is>
           <t>3348452263.6</t>
         </is>
       </c>
-      <c r="AZ73" t="inlineStr">
-        <is>
-          <t>6518094899.78</t>
-        </is>
+      <c r="AZ73" t="n">
+        <v>6518094899.78</v>
       </c>
       <c r="BA73" t="inlineStr">
         <is>
@@ -32098,8 +31664,10 @@
           <t>-269801426.3338051</t>
         </is>
       </c>
-      <c r="BD73" t="n">
-        <v>5022784742</v>
+      <c r="BD73" t="inlineStr">
+        <is>
+          <t>5022784742.0</t>
+        </is>
       </c>
       <c r="BE73" t="inlineStr">
         <is>
@@ -32265,7 +31833,7 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
@@ -32449,15 +32017,11 @@
           <t>162.1</t>
         </is>
       </c>
-      <c r="AM74" t="inlineStr">
-        <is>
-          <t>171.55</t>
-        </is>
-      </c>
-      <c r="AN74" t="inlineStr">
-        <is>
-          <t>166.67</t>
-        </is>
+      <c r="AM74" t="n">
+        <v>171.55</v>
+      </c>
+      <c r="AN74" t="n">
+        <v>166.67</v>
       </c>
       <c r="AO74" t="inlineStr">
         <is>
@@ -32504,20 +32068,16 @@
           <t>7649479589.0</t>
         </is>
       </c>
-      <c r="AX74" t="inlineStr">
-        <is>
-          <t>3747950110.4</t>
-        </is>
+      <c r="AX74" t="n">
+        <v>3747950110.4</v>
       </c>
       <c r="AY74" t="inlineStr">
         <is>
           <t>3187753716.9</t>
         </is>
       </c>
-      <c r="AZ74" t="inlineStr">
-        <is>
-          <t>6448828659.12</t>
-        </is>
+      <c r="AZ74" t="n">
+        <v>6448828659.12</v>
       </c>
       <c r="BA74" t="inlineStr">
         <is>
@@ -32534,8 +32094,10 @@
           <t>-366978329.6306791</t>
         </is>
       </c>
-      <c r="BD74" t="n">
-        <v>7649479589</v>
+      <c r="BD74" t="inlineStr">
+        <is>
+          <t>7649479589.0</t>
+        </is>
       </c>
       <c r="BE74" t="inlineStr">
         <is>
@@ -32701,7 +32263,7 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
@@ -32885,15 +32447,11 @@
           <t>164.7</t>
         </is>
       </c>
-      <c r="AM75" t="inlineStr">
-        <is>
-          <t>172.05</t>
-        </is>
-      </c>
-      <c r="AN75" t="inlineStr">
-        <is>
-          <t>166.08</t>
-        </is>
+      <c r="AM75" t="n">
+        <v>172.05</v>
+      </c>
+      <c r="AN75" t="n">
+        <v>166.08</v>
       </c>
       <c r="AO75" t="inlineStr">
         <is>
@@ -32940,20 +32498,16 @@
           <t>2918829265.0</t>
         </is>
       </c>
-      <c r="AX75" t="inlineStr">
-        <is>
-          <t>2774570723.0</t>
-        </is>
+      <c r="AX75" t="n">
+        <v>2774570723</v>
       </c>
       <c r="AY75" t="inlineStr">
         <is>
           <t>3016948267.5</t>
         </is>
       </c>
-      <c r="AZ75" t="inlineStr">
-        <is>
-          <t>6307955645.82</t>
-        </is>
+      <c r="AZ75" t="n">
+        <v>6307955645.82</v>
       </c>
       <c r="BA75" t="inlineStr">
         <is>
@@ -32970,8 +32524,10 @@
           <t>-774127699.0322614</t>
         </is>
       </c>
-      <c r="BD75" t="n">
-        <v>2918829265</v>
+      <c r="BD75" t="inlineStr">
+        <is>
+          <t>2918829265.0</t>
+        </is>
       </c>
       <c r="BE75" t="inlineStr">
         <is>
@@ -33137,7 +32693,7 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
@@ -33321,15 +32877,11 @@
           <t>166.0</t>
         </is>
       </c>
-      <c r="AM76" t="inlineStr">
-        <is>
-          <t>172.2</t>
-        </is>
-      </c>
-      <c r="AN76" t="inlineStr">
-        <is>
-          <t>165.33</t>
-        </is>
+      <c r="AM76" t="n">
+        <v>172.2</v>
+      </c>
+      <c r="AN76" t="n">
+        <v>165.33</v>
       </c>
       <c r="AO76" t="inlineStr">
         <is>
@@ -33376,20 +32928,16 @@
           <t>3371858763.0</t>
         </is>
       </c>
-      <c r="AX76" t="inlineStr">
-        <is>
-          <t>2612557535.8</t>
-        </is>
+      <c r="AX76" t="n">
+        <v>2612557535.8</v>
       </c>
       <c r="AY76" t="inlineStr">
         <is>
           <t>3246709810.3</t>
         </is>
       </c>
-      <c r="AZ76" t="inlineStr">
-        <is>
-          <t>6279997636.12</t>
-        </is>
+      <c r="AZ76" t="n">
+        <v>6279997636.12</v>
       </c>
       <c r="BA76" t="inlineStr">
         <is>
@@ -33406,8 +32954,10 @@
           <t>-821266845.6405125</t>
         </is>
       </c>
-      <c r="BD76" t="n">
-        <v>3371858763</v>
+      <c r="BD76" t="inlineStr">
+        <is>
+          <t>3371858763.0</t>
+        </is>
       </c>
       <c r="BE76" t="inlineStr">
         <is>
@@ -33573,7 +33123,7 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
@@ -33757,15 +33307,11 @@
           <t>166.8</t>
         </is>
       </c>
-      <c r="AM77" t="inlineStr">
-        <is>
-          <t>172.52</t>
-        </is>
-      </c>
-      <c r="AN77" t="inlineStr">
-        <is>
-          <t>164.6</t>
-        </is>
+      <c r="AM77" t="n">
+        <v>172.52</v>
+      </c>
+      <c r="AN77" t="n">
+        <v>164.6</v>
       </c>
       <c r="AO77" t="inlineStr">
         <is>
@@ -33812,20 +33358,16 @@
           <t>3031713588.0</t>
         </is>
       </c>
-      <c r="AX77" t="inlineStr">
-        <is>
-          <t>2341754288.4</t>
-        </is>
+      <c r="AX77" t="n">
+        <v>2341754288.4</v>
       </c>
       <c r="AY77" t="inlineStr">
         <is>
           <t>3717183320.3</t>
         </is>
       </c>
-      <c r="AZ77" t="inlineStr">
-        <is>
-          <t>6247764195.28</t>
-        </is>
+      <c r="AZ77" t="n">
+        <v>6247764195.28</v>
       </c>
       <c r="BA77" t="inlineStr">
         <is>
@@ -33842,8 +33384,10 @@
           <t>-907816399.6651387</t>
         </is>
       </c>
-      <c r="BD77" t="n">
-        <v>3031713588</v>
+      <c r="BD77" t="inlineStr">
+        <is>
+          <t>3031713588.0</t>
+        </is>
       </c>
       <c r="BE77" t="inlineStr">
         <is>
@@ -34009,7 +33553,7 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
@@ -34193,15 +33737,11 @@
           <t>167.7</t>
         </is>
       </c>
-      <c r="AM78" t="inlineStr">
-        <is>
-          <t>172.38</t>
-        </is>
-      </c>
-      <c r="AN78" t="inlineStr">
-        <is>
-          <t>163.91</t>
-        </is>
+      <c r="AM78" t="n">
+        <v>172.38</v>
+      </c>
+      <c r="AN78" t="n">
+        <v>163.91</v>
       </c>
       <c r="AO78" t="inlineStr">
         <is>
@@ -34248,20 +33788,16 @@
           <t>1767869347.0</t>
         </is>
       </c>
-      <c r="AX78" t="inlineStr">
-        <is>
-          <t>2297971337.8</t>
-        </is>
+      <c r="AX78" t="n">
+        <v>2297971337.8</v>
       </c>
       <c r="AY78" t="inlineStr">
         <is>
           <t>5310238320.6</t>
         </is>
       </c>
-      <c r="AZ78" t="inlineStr">
-        <is>
-          <t>6248161668.22</t>
-        </is>
+      <c r="AZ78" t="n">
+        <v>6248161668.22</v>
       </c>
       <c r="BA78" t="inlineStr">
         <is>
@@ -34278,8 +33814,10 @@
           <t>-962592479.5337062</t>
         </is>
       </c>
-      <c r="BD78" t="n">
-        <v>1767869347</v>
+      <c r="BD78" t="inlineStr">
+        <is>
+          <t>1767869347.0</t>
+        </is>
       </c>
       <c r="BE78" t="inlineStr">
         <is>
